--- a/data/trans_orig/IPAQ_MET-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86364</t>
+          <t>84841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121930</t>
+          <t>121472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49743</t>
+          <t>48641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119950</t>
+          <t>119985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163054</t>
+          <t>163742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196135</t>
+          <t>197684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237190</t>
+          <t>238384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180572</t>
+          <t>182531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219197</t>
+          <t>218787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>391063</t>
+          <t>387088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>447159</t>
+          <t>445332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82820</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117735</t>
+          <t>116669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139889</t>
+          <t>139006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>175961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232801</t>
+          <t>230513</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283391</t>
+          <t>284138</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103422</t>
+          <t>103710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143515</t>
+          <t>143454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55023</t>
+          <t>54126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141519</t>
+          <t>140834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188852</t>
+          <t>188868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>285888</t>
+          <t>285146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>333239</t>
+          <t>332640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>272907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>318386</t>
+          <t>319712</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>570844</t>
+          <t>569754</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>638722</t>
+          <t>637745</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137837</t>
+          <t>137250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179777</t>
+          <t>182087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206787</t>
+          <t>204991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249786</t>
+          <t>250492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>354475</t>
+          <t>358290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>417698</t>
+          <t>420841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91693</t>
+          <t>91613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130134</t>
+          <t>129574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>37229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>64045</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138904</t>
+          <t>137112</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>184542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>269268</t>
+          <t>272963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323370</t>
+          <t>324394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>314299</t>
+          <t>311201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364117</t>
+          <t>361442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>595897</t>
+          <t>598956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>664664</t>
+          <t>669898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236949</t>
+          <t>238651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289419</t>
+          <t>286943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247910</t>
+          <t>249889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297373</t>
+          <t>300783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502885</t>
+          <t>502280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>571351</t>
+          <t>574236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87790</t>
+          <t>87181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92621</t>
+          <t>92895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135800</t>
+          <t>135389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>298843</t>
+          <t>296889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350521</t>
+          <t>352074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327109</t>
+          <t>328915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379213</t>
+          <t>381072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>637528</t>
+          <t>640120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>716339</t>
+          <t>718169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225657</t>
+          <t>224490</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>278843</t>
+          <t>278758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228050</t>
+          <t>224475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>278927</t>
+          <t>277304</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>468130</t>
+          <t>463984</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>540330</t>
+          <t>540866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>54970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38712</t>
+          <t>38005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66088</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>252764</t>
+          <t>248870</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>297346</t>
+          <t>297077</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>215151</t>
+          <t>213973</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>262233</t>
+          <t>259743</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>480683</t>
+          <t>478163</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>549413</t>
+          <t>543759</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139919</t>
+          <t>140134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184387</t>
+          <t>182427</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224792</t>
+          <t>227877</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272634</t>
+          <t>273541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>382227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>444641</t>
+          <t>446450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27168</t>
+          <t>27340</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45155</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>162099</t>
+          <t>161461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199184</t>
+          <t>199635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>161764</t>
+          <t>160703</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>202013</t>
+          <t>201893</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>335647</t>
+          <t>336192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>389947</t>
+          <t>389929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116729</t>
+          <t>117676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154804</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160753</t>
+          <t>162054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201721</t>
+          <t>201722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>291929</t>
+          <t>290670</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>345100</t>
+          <t>343960</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>86032</t>
+          <t>88369</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116518</t>
+          <t>115067</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>81621</t>
+          <t>84224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123010</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179264</t>
+          <t>179349</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>226033</t>
+          <t>229193</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129450</t>
+          <t>129304</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>158796</t>
+          <t>156605</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>274955</t>
+          <t>273610</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>315137</t>
+          <t>313122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>415222</t>
+          <t>411908</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>464121</t>
+          <t>464625</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>431300</t>
+          <t>431703</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>514605</t>
+          <t>519223</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170450</t>
+          <t>174516</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>229257</t>
+          <t>229103</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>628634</t>
+          <t>627137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>727900</t>
+          <t>721698</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1650046</t>
+          <t>1643158</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1764295</t>
+          <t>1764424</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1647601</t>
+          <t>1643420</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1769596</t>
+          <t>1767983</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3335448</t>
+          <t>3329661</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3497079</t>
+          <t>3504877</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1159154</t>
+          <t>1156702</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1272711</t>
+          <t>1276134</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1580306</t>
+          <t>1583138</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1702492</t>
+          <t>1705041</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2760102</t>
+          <t>2762130</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2926261</t>
+          <t>2936171</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139538</t>
+          <t>134692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209571</t>
+          <t>204708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46881</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83371</t>
+          <t>86807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198414</t>
+          <t>197084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277012</t>
+          <t>274388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128542</t>
+          <t>134411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199002</t>
+          <t>201342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132786</t>
+          <t>131643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179433</t>
+          <t>180548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280679</t>
+          <t>281190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>363647</t>
+          <t>366430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39708</t>
+          <t>43051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>95701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74843</t>
+          <t>72764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117440</t>
+          <t>117009</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126768</t>
+          <t>124220</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>196613</t>
+          <t>191428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104658</t>
+          <t>107585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>152096</t>
+          <t>153828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108791</t>
+          <t>108722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165286</t>
+          <t>163984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248948</t>
+          <t>248564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163952</t>
+          <t>164090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>214461</t>
+          <t>213153</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>150969</t>
+          <t>143553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>274736</t>
+          <t>275991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>310821</t>
+          <t>314026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>464172</t>
+          <t>467122</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85011</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131803</t>
+          <t>131780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140569</t>
+          <t>138714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317929</t>
+          <t>317842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245364</t>
+          <t>240174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>456913</t>
+          <t>450922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116275</t>
+          <t>116550</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159023</t>
+          <t>159051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80827</t>
+          <t>78570</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123419</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>205311</t>
+          <t>204119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>272526</t>
+          <t>270348</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231400</t>
+          <t>231901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278935</t>
+          <t>279478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196239</t>
+          <t>187899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291113</t>
+          <t>291574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441742</t>
+          <t>444692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>555786</t>
+          <t>557053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122525</t>
+          <t>122789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166243</t>
+          <t>166693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186268</t>
+          <t>187420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>312539</t>
+          <t>324356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>325089</t>
+          <t>321474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>502054</t>
+          <t>481451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76279</t>
+          <t>77313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>248971</t>
+          <t>253152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117110</t>
+          <t>112932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>156414</t>
+          <t>154757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179913</t>
+          <t>205444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376627</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>394059</t>
+          <t>390686</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>738880</t>
+          <t>740364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283024</t>
+          <t>275931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>367671</t>
+          <t>365004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>726899</t>
+          <t>728729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1166082</t>
+          <t>1138274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>79952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>256999</t>
+          <t>255620</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204357</t>
+          <t>204955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>315855</t>
+          <t>332457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252684</t>
+          <t>262696</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>511774</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>109618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147369</t>
+          <t>146938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80341</t>
+          <t>80593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105226</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201141</t>
+          <t>200821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>245200</t>
+          <t>245808</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>223145</t>
+          <t>222613</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>266852</t>
+          <t>263864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246613</t>
+          <t>245765</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279375</t>
+          <t>282024</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>478018</t>
+          <t>478968</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>534808</t>
+          <t>534165</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>168754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212429</t>
+          <t>209174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>175557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209775</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>355311</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407148</t>
+          <t>411019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74674</t>
+          <t>74128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100430</t>
+          <t>100536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100187</t>
+          <t>99271</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>468655</t>
+          <t>453800</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>192096</t>
+          <t>190735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>640182</t>
+          <t>646272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>169167</t>
+          <t>168490</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199298</t>
+          <t>200158</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75999</t>
+          <t>86120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>287269</t>
+          <t>290203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>206081</t>
+          <t>196678</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>477969</t>
+          <t>477314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>83422</t>
+          <t>83663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110903</t>
+          <t>110943</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>65506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>229608</t>
+          <t>227048</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134116</t>
+          <t>132314</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>315594</t>
+          <t>317729</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48595</t>
+          <t>48703</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>29040</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45108</t>
+          <t>43993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62736</t>
+          <t>63312</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>86259</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -7463,12 +7463,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>120837</t>
+          <t>120750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>147494</t>
+          <t>147516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102169</t>
+          <t>104010</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>127648</t>
+          <t>131263</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230993</t>
+          <t>232459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>270499</t>
+          <t>268653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -7576,12 +7576,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98212</t>
+          <t>96811</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122601</t>
+          <t>123043</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>261141</t>
+          <t>259400</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>287766</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>364845</t>
+          <t>365342</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>404571</t>
+          <t>402812</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>675876</t>
+          <t>660524</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>955381</t>
+          <t>949804</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>612920</t>
+          <t>614839</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1350506</t>
+          <t>1330069</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1445155</t>
+          <t>1448214</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2261008</t>
+          <t>2185213</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1553253</t>
+          <t>1552122</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2096743</t>
+          <t>2102696</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1248509</t>
+          <t>1251571</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1665732</t>
+          <t>1676566</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2975144</t>
+          <t>2979549</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3659953</t>
+          <t>3636724</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>709136</t>
+          <t>695016</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>977738</t>
+          <t>982842</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1137216</t>
+          <t>1105479</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1515929</t>
+          <t>1503676</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1941472</t>
+          <t>1964527</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2457476</t>
+          <t>2459120</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IPAQ_MET-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84841</t>
+          <t>85898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121472</t>
+          <t>121510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48641</t>
+          <t>49855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119985</t>
+          <t>118702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163742</t>
+          <t>162804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197684</t>
+          <t>197139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238384</t>
+          <t>237014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182531</t>
+          <t>180507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218787</t>
+          <t>219542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387088</t>
+          <t>391445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>445332</t>
+          <t>448996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81313</t>
+          <t>83037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116669</t>
+          <t>117242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139006</t>
+          <t>139816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175961</t>
+          <t>177235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230513</t>
+          <t>228424</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>284138</t>
+          <t>284836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103710</t>
+          <t>104853</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143454</t>
+          <t>144205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54126</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140834</t>
+          <t>142218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188868</t>
+          <t>186540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>285146</t>
+          <t>285154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>332640</t>
+          <t>334557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>272907</t>
+          <t>269132</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>319712</t>
+          <t>315659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>569754</t>
+          <t>568165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>637745</t>
+          <t>635655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137250</t>
+          <t>137559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182087</t>
+          <t>179879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204991</t>
+          <t>207653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>250492</t>
+          <t>252060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358290</t>
+          <t>358161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420841</t>
+          <t>420839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91613</t>
+          <t>91546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129574</t>
+          <t>132583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37229</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64045</t>
+          <t>64582</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137112</t>
+          <t>138239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>184542</t>
+          <t>184589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272963</t>
+          <t>273232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324394</t>
+          <t>324783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311201</t>
+          <t>314108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361442</t>
+          <t>361429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>598956</t>
+          <t>597670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>669898</t>
+          <t>670649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238651</t>
+          <t>238423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286943</t>
+          <t>288107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249889</t>
+          <t>250350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300783</t>
+          <t>298542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502280</t>
+          <t>501054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574236</t>
+          <t>573534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>55011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87181</t>
+          <t>88759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>56807</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92895</t>
+          <t>94168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135389</t>
+          <t>134999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296889</t>
+          <t>297928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352074</t>
+          <t>349766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328915</t>
+          <t>327575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381072</t>
+          <t>379053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>640120</t>
+          <t>644475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718169</t>
+          <t>717964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>224490</t>
+          <t>228273</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>278758</t>
+          <t>278015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>224475</t>
+          <t>227116</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>277304</t>
+          <t>277725</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>463984</t>
+          <t>466309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>540866</t>
+          <t>540319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>30006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54970</t>
+          <t>55765</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>17825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>67353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>248870</t>
+          <t>251971</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>297077</t>
+          <t>296943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>213973</t>
+          <t>212741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>259743</t>
+          <t>260823</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>478163</t>
+          <t>476932</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>543759</t>
+          <t>549147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140134</t>
+          <t>140844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182427</t>
+          <t>183892</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227877</t>
+          <t>227135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>273541</t>
+          <t>274555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382227</t>
+          <t>373807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446450</t>
+          <t>443454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27340</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161461</t>
+          <t>162394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199635</t>
+          <t>199178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>160703</t>
+          <t>163346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>201893</t>
+          <t>202763</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336192</t>
+          <t>336495</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>389929</t>
+          <t>390865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117676</t>
+          <t>118305</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155325</t>
+          <t>154580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162054</t>
+          <t>162599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201722</t>
+          <t>201383</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>290670</t>
+          <t>290273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343960</t>
+          <t>345343</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88369</t>
+          <t>87117</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115067</t>
+          <t>114019</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84224</t>
+          <t>82500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122776</t>
+          <t>122686</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179349</t>
+          <t>179746</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>229193</t>
+          <t>228899</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129304</t>
+          <t>129239</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>156605</t>
+          <t>157662</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>273610</t>
+          <t>274040</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>313122</t>
+          <t>314612</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>411908</t>
+          <t>413789</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>464625</t>
+          <t>463843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>431703</t>
+          <t>433555</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>519223</t>
+          <t>516862</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>171304</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>229103</t>
+          <t>226488</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>627137</t>
+          <t>627220</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>721698</t>
+          <t>728740</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1643158</t>
+          <t>1651810</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1764424</t>
+          <t>1764368</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1643420</t>
+          <t>1649162</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1767983</t>
+          <t>1775590</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3329661</t>
+          <t>3334207</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3504877</t>
+          <t>3501877</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1156702</t>
+          <t>1155204</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1276134</t>
+          <t>1273174</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1583138</t>
+          <t>1575446</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1705041</t>
+          <t>1699591</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2762130</t>
+          <t>2770569</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2936171</t>
+          <t>2931303</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -4609,32 +4609,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>171189</t>
+          <t>174874</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134692</t>
+          <t>142350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204708</t>
+          <t>203950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4644,32 +4644,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>79338</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46099</t>
+          <t>59842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86807</t>
+          <t>102199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4679,32 +4679,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>235006</t>
+          <t>254212</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197084</t>
+          <t>215363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>274388</t>
+          <t>294614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -4722,32 +4722,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>165155</t>
+          <t>173874</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134411</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201342</t>
+          <t>205193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4757,32 +4757,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155168</t>
+          <t>176479</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180548</t>
+          <t>198418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4792,32 +4792,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>320323</t>
+          <t>350353</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281190</t>
+          <t>311898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>366430</t>
+          <t>391082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -4835,32 +4835,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63643</t>
+          <t>59045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95701</t>
+          <t>85694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4870,32 +4870,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94215</t>
+          <t>106695</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72764</t>
+          <t>85313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117009</t>
+          <t>132305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4905,32 +4905,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>157858</t>
+          <t>165740</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>124220</t>
+          <t>134094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>191428</t>
+          <t>199452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4983,17 +4983,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5018,17 +5018,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5065,32 +5065,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>128129</t>
+          <t>147565</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107585</t>
+          <t>122984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153828</t>
+          <t>175734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5100,32 +5100,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85590</t>
+          <t>92880</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52859</t>
+          <t>75036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108722</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5135,32 +5135,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>213719</t>
+          <t>240445</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163984</t>
+          <t>209805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248564</t>
+          <t>274799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -5178,32 +5178,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>188381</t>
+          <t>214797</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164090</t>
+          <t>186092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>213153</t>
+          <t>244339</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>229499</t>
+          <t>260803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143553</t>
+          <t>237070</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>275991</t>
+          <t>285176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5248,32 +5248,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>417880</t>
+          <t>475600</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314026</t>
+          <t>437937</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>467122</t>
+          <t>512081</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -5291,32 +5291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>107037</t>
+          <t>114528</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>90108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131780</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>197005</t>
+          <t>148050</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138714</t>
+          <t>128693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317842</t>
+          <t>169588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>304041</t>
+          <t>262578</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>240174</t>
+          <t>232098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450922</t>
+          <t>301842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -5404,17 +5404,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5439,17 +5439,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5474,17 +5474,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5521,32 +5521,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136516</t>
+          <t>153527</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116550</t>
+          <t>133602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159051</t>
+          <t>179299</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5556,32 +5556,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>105399</t>
+          <t>116718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78570</t>
+          <t>100845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123763</t>
+          <t>133149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5591,32 +5591,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>241915</t>
+          <t>270245</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>204119</t>
+          <t>244537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>270348</t>
+          <t>299006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -5634,32 +5634,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>256725</t>
+          <t>296243</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231901</t>
+          <t>266338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279478</t>
+          <t>318839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5669,32 +5669,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>260320</t>
+          <t>300744</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187899</t>
+          <t>281149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291574</t>
+          <t>323184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5704,32 +5704,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>517045</t>
+          <t>596987</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444692</t>
+          <t>563216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>557053</t>
+          <t>631166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -5747,32 +5747,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>171068</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122789</t>
+          <t>148469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166693</t>
+          <t>198403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5782,32 +5782,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>226283</t>
+          <t>205731</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187420</t>
+          <t>185429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324356</t>
+          <t>227557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5817,32 +5817,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>369380</t>
+          <t>376798</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321474</t>
+          <t>346346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481451</t>
+          <t>410030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -5860,17 +5860,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5895,17 +5895,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5930,17 +5930,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5977,32 +5977,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>172830</t>
+          <t>196296</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77313</t>
+          <t>171914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>253152</t>
+          <t>222240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>137897</t>
+          <t>152362</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112932</t>
+          <t>134521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154757</t>
+          <t>169471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>310726</t>
+          <t>348658</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205444</t>
+          <t>319628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>378518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6090,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>537513</t>
+          <t>309782</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>390686</t>
+          <t>280593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>740364</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6125,32 +6125,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>339067</t>
+          <t>365358</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275931</t>
+          <t>343063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365004</t>
+          <t>387551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6160,32 +6160,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>876580</t>
+          <t>675140</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>728729</t>
+          <t>641109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1138274</t>
+          <t>709019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -6203,32 +6203,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>177443</t>
+          <t>194539</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79952</t>
+          <t>170942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255620</t>
+          <t>222275</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6238,32 +6238,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>235918</t>
+          <t>219166</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204955</t>
+          <t>200641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>332457</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6273,32 +6273,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>413361</t>
+          <t>413706</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>262696</t>
+          <t>383603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>512002</t>
+          <t>448536</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -6316,17 +6316,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6351,17 +6351,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6386,17 +6386,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>128347</t>
+          <t>142715</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109618</t>
+          <t>125214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146938</t>
+          <t>162746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6468,32 +6468,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>92625</t>
+          <t>100911</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>87680</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>115822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>220972</t>
+          <t>243627</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200821</t>
+          <t>220401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>245808</t>
+          <t>269620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -6546,32 +6546,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>243525</t>
+          <t>261036</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222613</t>
+          <t>237692</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>263864</t>
+          <t>282753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6581,32 +6581,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>262681</t>
+          <t>294862</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245765</t>
+          <t>276336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>282024</t>
+          <t>314915</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6616,32 +6616,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>506206</t>
+          <t>555899</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>478968</t>
+          <t>529901</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>534165</t>
+          <t>585457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -6659,17 +6659,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>189361</t>
+          <t>205594</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>168754</t>
+          <t>183053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>209174</t>
+          <t>227526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6694,67 +6694,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>192599</t>
+          <t>213081</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175557</t>
+          <t>195564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210318</t>
+          <t>233682</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>418676</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>390332</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>447318</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>34,37%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>32,04%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>381960</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>355965</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>411019</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>34,44%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6807,17 +6807,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6842,17 +6842,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>87246</t>
+          <t>98193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74128</t>
+          <t>83810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>274770</t>
+          <t>76263</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99271</t>
+          <t>65745</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>453800</t>
+          <t>88625</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>362017</t>
+          <t>174455</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>190735</t>
+          <t>154790</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>646272</t>
+          <t>194513</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -7002,32 +7002,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>184422</t>
+          <t>201409</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168490</t>
+          <t>184113</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>200158</t>
+          <t>219835</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7037,32 +7037,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86120</t>
+          <t>186489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>290203</t>
+          <t>219039</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7072,32 +7072,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>371246</t>
+          <t>404019</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196678</t>
+          <t>381679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>477314</t>
+          <t>427004</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -7115,32 +7115,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>96497</t>
+          <t>107478</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>83663</t>
+          <t>92644</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110943</t>
+          <t>121737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7150,32 +7150,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>146774</t>
+          <t>160293</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65506</t>
+          <t>145178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227048</t>
+          <t>177016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7185,32 +7185,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>243271</t>
+          <t>267772</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132314</t>
+          <t>248608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317729</t>
+          <t>287294</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -7228,17 +7228,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>38648</t>
+          <t>43039</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29101</t>
+          <t>33593</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48703</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43993</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>68530</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86259</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -7458,32 +7458,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>134110</t>
+          <t>147530</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>120750</t>
+          <t>133818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>147516</t>
+          <t>163999</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7493,32 +7493,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>115639</t>
+          <t>127725</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>104010</t>
+          <t>114277</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>131263</t>
+          <t>142517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7528,32 +7528,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>249749</t>
+          <t>275255</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>232459</t>
+          <t>254946</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268653</t>
+          <t>294711</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -7571,32 +7571,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>110001</t>
+          <t>119629</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96811</t>
+          <t>105438</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123043</t>
+          <t>134724</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7606,27 +7606,27 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>274377</t>
+          <t>298547</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>259400</t>
+          <t>283279</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>287766</t>
+          <t>313999</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7641,32 +7641,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>384378</t>
+          <t>418176</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>365342</t>
+          <t>396722</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>402812</t>
+          <t>437914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -7684,17 +7684,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7719,17 +7719,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7754,17 +7754,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>862906</t>
+          <t>956209</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>660524</t>
+          <t>894221</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>949804</t>
+          <t>1016672</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>795913</t>
+          <t>656809</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>614839</t>
+          <t>614961</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1330069</t>
+          <t>698409</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1658818</t>
+          <t>1613018</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1448214</t>
+          <t>1533502</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2185213</t>
+          <t>1689215</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -7914,32 +7914,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1709833</t>
+          <t>1604671</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1552122</t>
+          <t>1535821</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2102696</t>
+          <t>1672184</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7949,32 +7949,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1549197</t>
+          <t>1728581</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1251571</t>
+          <t>1675636</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1676566</t>
+          <t>1783736</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7984,32 +7984,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3259029</t>
+          <t>3333252</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2979549</t>
+          <t>3244926</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3636724</t>
+          <t>3423196</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -8027,32 +8027,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>887079</t>
+          <t>971882</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>695016</t>
+          <t>915832</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>982842</t>
+          <t>1031606</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8062,32 +8062,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1367171</t>
+          <t>1351564</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1105479</t>
+          <t>1300256</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1503676</t>
+          <t>1402984</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8097,32 +8097,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2254249</t>
+          <t>2323446</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1964527</t>
+          <t>2242562</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2459120</t>
+          <t>2402306</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -8140,17 +8140,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8175,17 +8175,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8210,17 +8210,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
